--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.18408167606572</v>
+        <v>6.042413272360679</v>
       </c>
       <c r="D2" t="n">
-        <v>36.33556236985574</v>
+        <v>5.904528885101557</v>
       </c>
       <c r="E2" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F2" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.32581761309123</v>
+        <v>11.75294536212733</v>
       </c>
       <c r="D3" t="n">
-        <v>71.21435162570529</v>
+        <v>11.57233213917711</v>
       </c>
       <c r="E3" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F3" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.8355264221469</v>
+        <v>7.935773043598871</v>
       </c>
       <c r="D4" t="n">
-        <v>48.14547734743289</v>
+        <v>7.823640068957845</v>
       </c>
       <c r="E4" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F4" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.00773530772068</v>
+        <v>4.38875698750461</v>
       </c>
       <c r="D5" t="n">
-        <v>26.15852615048972</v>
+        <v>4.25076049945458</v>
       </c>
       <c r="E5" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F5" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.40749230125134</v>
+        <v>9.166217498953342</v>
       </c>
       <c r="D6" t="n">
-        <v>55.15191173629488</v>
+        <v>8.96218565714792</v>
       </c>
       <c r="E6" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F6" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.12450451686398</v>
+        <v>3.270231983990397</v>
       </c>
       <c r="D7" t="n">
-        <v>19.71921884134182</v>
+        <v>3.204373061718046</v>
       </c>
       <c r="E7" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F7" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.98784340981981</v>
+        <v>6.335524554095719</v>
       </c>
       <c r="D8" t="n">
-        <v>39.70575291451571</v>
+        <v>6.452184848608804</v>
       </c>
       <c r="E8" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F8" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.01473283752835</v>
+        <v>8.452394086098357</v>
       </c>
       <c r="D9" t="n">
-        <v>50.99466508521894</v>
+        <v>8.286633076348078</v>
       </c>
       <c r="E9" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F9" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>52.85492490222413</v>
+        <v>8.588925296611421</v>
       </c>
       <c r="D10" t="n">
-        <v>52.63447860409278</v>
+        <v>8.553102773165078</v>
       </c>
       <c r="E10" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F10" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.39425728704094</v>
+        <v>5.426566809144153</v>
       </c>
       <c r="D11" t="n">
-        <v>33.9138459037796</v>
+        <v>5.510999959364185</v>
       </c>
       <c r="E11" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F11" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.45862573527369</v>
+        <v>6.087026681981974</v>
       </c>
       <c r="D12" t="n">
-        <v>36.98900948624045</v>
+        <v>6.010714041514073</v>
       </c>
       <c r="E12" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F12" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5.947807978834427</v>
+        <v>0.9665187965605944</v>
       </c>
       <c r="D13" t="n">
-        <v>6.38538850889671</v>
+        <v>1.037625632695715</v>
       </c>
       <c r="E13" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F13" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>11.48187449157487</v>
+        <v>1.865804604880917</v>
       </c>
       <c r="D14" t="n">
-        <v>12.19987089456705</v>
+        <v>1.982479020367146</v>
       </c>
       <c r="E14" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F14" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.63836543057133</v>
+        <v>3.516234382467842</v>
       </c>
       <c r="D15" t="n">
-        <v>22.52816897715284</v>
+        <v>3.660827458787337</v>
       </c>
       <c r="E15" t="n">
-        <v>17.91705645129594</v>
+        <v>2.91152167333559</v>
       </c>
       <c r="F15" t="n">
-        <v>17.43826092982214</v>
+        <v>2.833717401096097</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
